--- a/output/pdf_financials_xlsx/CU.xlsx
+++ b/output/pdf_financials_xlsx/CU.xlsx
@@ -3024,19 +3024,19 @@
         <v>36</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>215</v>
+        <v>328</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>66</v>
+        <v>602</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>35</v>
+        <v>368</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>30</v>
+        <v>432</v>
       </c>
     </row>
     <row r="76">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">

--- a/output/pdf_financials_xlsx/CU.xlsx
+++ b/output/pdf_financials_xlsx/CU.xlsx
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -1389,31 +1389,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>694</v>
+        <v>672</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>866</v>
+        <v>839</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>915</v>
+        <v>861</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>624</v>
+        <v>548</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>202</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>915</v>
+        <v>861</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>624</v>
+        <v>548</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>202</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8.590761988820242</v>
+        <v>8.208296557811121</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.350061199510404</v>
+        <v>1.811505507955936</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.20904729266621</v>
+        <v>4.592186429061001</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.98591549295775</v>
+        <v>10.34571062740077</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.30583214793741</v>
+        <v>14.99288762446657</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>20.70158102766798</v>
+        <v>19.81225296442688</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>24.10432033719705</v>
+        <v>22.68177028451001</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>16.67557455905933</v>
+        <v>14.64457509353287</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.474254742547426</v>
+        <v>4.037940379403794</v>
       </c>
     </row>
     <row r="31">
@@ -2076,31 +2076,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>129</v>
+        <v>1226</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>76</v>
+        <v>707</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>188</v>
+        <v>957</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>261</v>
+        <v>1145</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>211</v>
+        <v>966</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>136</v>
+        <v>849</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>171</v>
+        <v>700</v>
       </c>
     </row>
     <row r="49">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" s="5" t="n">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">

--- a/output/pdf_financials_xlsx/CU.xlsx
+++ b/output/pdf_financials_xlsx/CU.xlsx
@@ -823,31 +823,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>382</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>409</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>469</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>462</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>402</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>371</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>406</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>432</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14">
@@ -1389,31 +1389,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>852</v>
+        <v>470</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>672</v>
+        <v>263</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>839</v>
+        <v>370</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>986</v>
+        <v>524</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>527</v>
+        <v>125</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>802</v>
+        <v>431</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>861</v>
+        <v>455</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>548</v>
+        <v>116</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>149</v>
+        <v>-309</v>
       </c>
     </row>
     <row r="28">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>279</v>
+        <v>-103</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>74</v>
+        <v>-335</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>201</v>
+        <v>-268</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>404</v>
+        <v>-58</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>527</v>
+        <v>125</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>802</v>
+        <v>431</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>861</v>
+        <v>455</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>548</v>
+        <v>116</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>149</v>
+        <v>-309</v>
       </c>
     </row>
     <row r="30">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8.208296557811121</v>
+        <v>-3.03030303030303</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.811505507955936</v>
+        <v>-8.200734394124847</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.592186429061001</v>
+        <v>-6.122915238748001</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.34571062740077</v>
+        <v>-1.48527528809219</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.99288762446657</v>
+        <v>3.556187766714083</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.81225296442688</v>
+        <v>10.64723320158103</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22.68177028451001</v>
+        <v>11.98630136986301</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>14.64457509353287</v>
+        <v>3.099946552645644</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.037940379403794</v>
+        <v>-8.373983739837399</v>
       </c>
     </row>
     <row r="31">
@@ -4243,31 +4243,31 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -4719,31 +4719,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="127">
@@ -16147,7 +16147,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>15</v>
       </c>
@@ -17051,7 +17055,11 @@
           <t>Dividends paid to non-controlling interests 28</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -19070,7 +19078,11 @@
           <t>Dividends paid to non-controlling interests 27</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -20270,7 +20282,11 @@
           <t>Dividends paid to non-controlling interests 30</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -21126,7 +21142,11 @@
           <t>Proceeds on disposal of property, plant and equipment 4</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -22171,7 +22191,11 @@
           <t>Dividends paid to non-controlling interests 34 (7)</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -23635,7 +23659,11 @@
           <t>Dividends paid to non-controlling interests 32</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
         <v>-7</v>
       </c>
@@ -24738,7 +24766,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E331" s="5" t="n">
         <v>-382</v>
       </c>

--- a/output/pdf_financials_xlsx/CU.xlsx
+++ b/output/pdf_financials_xlsx/CU.xlsx
@@ -2851,22 +2851,22 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
@@ -2885,22 +2885,22 @@
         <v>175</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -3024,19 +3024,19 @@
         <v>36</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="76">
@@ -3191,22 +3191,22 @@
         <v>1.597074062785736</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1.302557433896836</v>
+        <v>1.303857824013871</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1.401055408970976</v>
+        <v>1.402081501026092</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1.356354373054062</v>
+        <v>1.357345032550241</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1.478619340413639</v>
+        <v>1.479737283398547</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.524224125825025</v>
+        <v>1.525347563544446</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>1.872234010306153</v>
+        <v>1.873598060018187</v>
       </c>
     </row>
     <row r="81">
@@ -6288,7 +6288,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -7860,7 +7864,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -9137,7 +9145,11 @@
           <t>Lease liabilities 16</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -10595,7 +10607,11 @@
           <t>Lease liabilities 3,19</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
